--- a/artfynd/A 5403-2024 artfynd.xlsx
+++ b/artfynd/A 5403-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2252,6 +2252,1307 @@
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120467979</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91542</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4786</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Mandelriska</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lactifluus volemus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Kuntze</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Keddebo-Bön, Dls</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>311463</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6525779</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Töftedal</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120467944</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57473</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Keddebo-Bön, Dls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>311432</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6525830</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Töftedal</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ett par i sitt hemvist och häckningsrevir</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120467953</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79160</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Keddebo-Bön, Dls</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>311463</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6525829</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Töftedal</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120467927</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79160</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Keddebo-Bön, Dls</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>311401</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6525852</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Töftedal</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120468042</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79160</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Keddebo-Bön, Dls</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>311502</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6525831</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Töftedal</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120467973</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Keddebo-Bön, Dls</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>311464</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6525792</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Töftedal</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120467916</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79160</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Keddebo-Bön, Dls</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>311367</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6525824</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Töftedal</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120468030</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Keddebo-Bön, Dls</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>311502</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6525831</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Töftedal</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120467983</v>
+      </c>
+      <c r="B25" t="n">
+        <v>90351</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Keddebo-Bön, Dls</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>311463</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6525779</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Töftedal</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120468047</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Keddebo-Bön, Dls</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>311532</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6525858</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Töftedal</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120467994</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79160</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Keddebo-Bön, Dls</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>311488</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6525797</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Töftedal</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120467986</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79160</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Keddebo-Bön, Dls</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>311465</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6525748</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Töftedal</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5403-2024 artfynd.xlsx
+++ b/artfynd/A 5403-2024 artfynd.xlsx
@@ -2254,10 +2254,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120467979</v>
+        <v>120467973</v>
       </c>
       <c r="B17" t="n">
-        <v>91542</v>
+        <v>91858</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2270,24 +2270,28 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4786</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lactifluus volemus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Kuntze</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2297,10 +2301,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>311463</v>
+        <v>311464</v>
       </c>
       <c r="R17" t="n">
-        <v>6525779</v>
+        <v>6525792</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2360,10 +2364,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120467944</v>
+        <v>120467927</v>
       </c>
       <c r="B18" t="n">
-        <v>57473</v>
+        <v>79160</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2376,39 +2380,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2416,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>311432</v>
+        <v>311401</v>
       </c>
       <c r="R18" t="n">
-        <v>6525830</v>
+        <v>6525852</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2454,17 +2445,13 @@
           <t>2024-10-16</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ett par i sitt hemvist och häckningsrevir</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2483,7 +2470,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120467953</v>
+        <v>120468042</v>
       </c>
       <c r="B19" t="n">
         <v>79160</v>
@@ -2526,10 +2513,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>311463</v>
+        <v>311502</v>
       </c>
       <c r="R19" t="n">
-        <v>6525829</v>
+        <v>6525831</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2589,10 +2576,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120467927</v>
+        <v>120468030</v>
       </c>
       <c r="B20" t="n">
-        <v>79160</v>
+        <v>57336</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2605,26 +2592,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2632,10 +2624,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>311401</v>
+        <v>311502</v>
       </c>
       <c r="R20" t="n">
-        <v>6525852</v>
+        <v>6525831</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2676,7 +2668,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2695,7 +2686,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120468042</v>
+        <v>120467953</v>
       </c>
       <c r="B21" t="n">
         <v>79160</v>
@@ -2738,10 +2729,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>311502</v>
+        <v>311463</v>
       </c>
       <c r="R21" t="n">
-        <v>6525831</v>
+        <v>6525829</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2801,10 +2792,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120467973</v>
+        <v>120467983</v>
       </c>
       <c r="B22" t="n">
-        <v>91858</v>
+        <v>90351</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2817,28 +2808,24 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>3215</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
@@ -2848,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>311464</v>
+        <v>311463</v>
       </c>
       <c r="R22" t="n">
-        <v>6525792</v>
+        <v>6525779</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2911,10 +2898,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120467916</v>
+        <v>120467944</v>
       </c>
       <c r="B23" t="n">
-        <v>79160</v>
+        <v>57473</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2927,26 +2914,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2954,10 +2954,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>311367</v>
+        <v>311432</v>
       </c>
       <c r="R23" t="n">
-        <v>6525824</v>
+        <v>6525830</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2992,13 +2992,17 @@
           <t>2024-10-16</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ett par i sitt hemvist och häckningsrevir</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3017,10 +3021,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120468030</v>
+        <v>120467979</v>
       </c>
       <c r="B24" t="n">
-        <v>57336</v>
+        <v>91542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3029,35 +3033,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>4786</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lactifluus volemus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) Kuntze</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3065,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>311502</v>
+        <v>311463</v>
       </c>
       <c r="R24" t="n">
-        <v>6525831</v>
+        <v>6525779</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3109,6 +3108,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3127,10 +3127,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120467983</v>
+        <v>120467916</v>
       </c>
       <c r="B25" t="n">
-        <v>90351</v>
+        <v>79160</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3139,25 +3139,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3215</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3170,10 +3170,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>311463</v>
+        <v>311367</v>
       </c>
       <c r="R25" t="n">
-        <v>6525779</v>
+        <v>6525824</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3233,10 +3233,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120468047</v>
+        <v>120467986</v>
       </c>
       <c r="B26" t="n">
-        <v>57336</v>
+        <v>79160</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3249,31 +3249,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3281,10 +3276,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>311532</v>
+        <v>311465</v>
       </c>
       <c r="R26" t="n">
-        <v>6525858</v>
+        <v>6525748</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3325,6 +3320,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3449,10 +3445,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120467986</v>
+        <v>120468047</v>
       </c>
       <c r="B28" t="n">
-        <v>79160</v>
+        <v>57336</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3465,26 +3461,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3492,10 +3493,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>311465</v>
+        <v>311532</v>
       </c>
       <c r="R28" t="n">
-        <v>6525748</v>
+        <v>6525858</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3536,7 +3537,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5403-2024 artfynd.xlsx
+++ b/artfynd/A 5403-2024 artfynd.xlsx
@@ -2254,10 +2254,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120467973</v>
+        <v>120467953</v>
       </c>
       <c r="B17" t="n">
-        <v>91858</v>
+        <v>79160</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2266,32 +2266,28 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2301,10 +2297,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>311464</v>
+        <v>311463</v>
       </c>
       <c r="R17" t="n">
-        <v>6525792</v>
+        <v>6525829</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2364,10 +2360,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120467927</v>
+        <v>120468030</v>
       </c>
       <c r="B18" t="n">
-        <v>79160</v>
+        <v>57336</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2380,26 +2376,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2407,10 +2408,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>311401</v>
+        <v>311502</v>
       </c>
       <c r="R18" t="n">
-        <v>6525852</v>
+        <v>6525831</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2451,7 +2452,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2470,10 +2470,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120468042</v>
+        <v>120467973</v>
       </c>
       <c r="B19" t="n">
-        <v>79160</v>
+        <v>91858</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2482,28 +2482,32 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -2513,10 +2517,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>311502</v>
+        <v>311464</v>
       </c>
       <c r="R19" t="n">
-        <v>6525831</v>
+        <v>6525792</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2576,10 +2580,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120468030</v>
+        <v>120467916</v>
       </c>
       <c r="B20" t="n">
-        <v>57336</v>
+        <v>79160</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2592,31 +2596,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2624,10 +2623,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>311502</v>
+        <v>311367</v>
       </c>
       <c r="R20" t="n">
-        <v>6525831</v>
+        <v>6525824</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2668,6 +2667,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2686,7 +2686,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120467953</v>
+        <v>120468042</v>
       </c>
       <c r="B21" t="n">
         <v>79160</v>
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>311463</v>
+        <v>311502</v>
       </c>
       <c r="R21" t="n">
-        <v>6525829</v>
+        <v>6525831</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2792,10 +2792,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120467983</v>
+        <v>120468047</v>
       </c>
       <c r="B22" t="n">
-        <v>90351</v>
+        <v>57336</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2804,30 +2804,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3215</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2835,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>311463</v>
+        <v>311532</v>
       </c>
       <c r="R22" t="n">
-        <v>6525779</v>
+        <v>6525858</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2879,7 +2884,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3021,10 +3025,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120467979</v>
+        <v>120467927</v>
       </c>
       <c r="B24" t="n">
-        <v>91542</v>
+        <v>79160</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3033,25 +3037,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4786</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lactifluus volemus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Kuntze</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3064,10 +3068,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>311463</v>
+        <v>311401</v>
       </c>
       <c r="R24" t="n">
-        <v>6525779</v>
+        <v>6525852</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3127,10 +3131,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120467916</v>
+        <v>120467983</v>
       </c>
       <c r="B25" t="n">
-        <v>79160</v>
+        <v>90351</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3139,25 +3143,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>3215</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3170,10 +3174,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>311367</v>
+        <v>311463</v>
       </c>
       <c r="R25" t="n">
-        <v>6525824</v>
+        <v>6525779</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3233,10 +3237,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120467986</v>
+        <v>120467979</v>
       </c>
       <c r="B26" t="n">
-        <v>79160</v>
+        <v>91542</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3245,25 +3249,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>4786</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lactifluus volemus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) Kuntze</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3276,10 +3280,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>311465</v>
+        <v>311463</v>
       </c>
       <c r="R26" t="n">
-        <v>6525748</v>
+        <v>6525779</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3339,7 +3343,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120467994</v>
+        <v>120467986</v>
       </c>
       <c r="B27" t="n">
         <v>79160</v>
@@ -3382,10 +3386,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>311488</v>
+        <v>311465</v>
       </c>
       <c r="R27" t="n">
-        <v>6525797</v>
+        <v>6525748</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3445,10 +3449,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120468047</v>
+        <v>120467994</v>
       </c>
       <c r="B28" t="n">
-        <v>57336</v>
+        <v>79160</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3461,31 +3465,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3493,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>311532</v>
+        <v>311488</v>
       </c>
       <c r="R28" t="n">
-        <v>6525858</v>
+        <v>6525797</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3537,6 +3536,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5403-2024 artfynd.xlsx
+++ b/artfynd/A 5403-2024 artfynd.xlsx
@@ -2686,10 +2686,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120468042</v>
+        <v>120468047</v>
       </c>
       <c r="B21" t="n">
-        <v>79160</v>
+        <v>57336</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2702,26 +2702,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2729,10 +2734,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>311502</v>
+        <v>311532</v>
       </c>
       <c r="R21" t="n">
-        <v>6525831</v>
+        <v>6525858</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2773,7 +2778,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2792,10 +2796,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120468047</v>
+        <v>120468042</v>
       </c>
       <c r="B22" t="n">
-        <v>57336</v>
+        <v>79160</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2808,31 +2812,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2840,10 +2839,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>311532</v>
+        <v>311502</v>
       </c>
       <c r="R22" t="n">
-        <v>6525858</v>
+        <v>6525831</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2884,6 +2883,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2902,10 +2902,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120467944</v>
+        <v>120467927</v>
       </c>
       <c r="B23" t="n">
-        <v>57473</v>
+        <v>79160</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2918,39 +2918,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2958,10 +2945,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>311432</v>
+        <v>311401</v>
       </c>
       <c r="R23" t="n">
-        <v>6525830</v>
+        <v>6525852</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2996,17 +2983,13 @@
           <t>2024-10-16</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ett par i sitt hemvist och häckningsrevir</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3025,10 +3008,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120467927</v>
+        <v>120467944</v>
       </c>
       <c r="B24" t="n">
-        <v>79160</v>
+        <v>57473</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3041,26 +3024,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3068,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>311401</v>
+        <v>311432</v>
       </c>
       <c r="R24" t="n">
-        <v>6525852</v>
+        <v>6525830</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3106,13 +3102,17 @@
           <t>2024-10-16</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ett par i sitt hemvist och häckningsrevir</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5403-2024 artfynd.xlsx
+++ b/artfynd/A 5403-2024 artfynd.xlsx
@@ -2254,7 +2254,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120467953</v>
+        <v>120467986</v>
       </c>
       <c r="B17" t="n">
         <v>79160</v>
@@ -2297,10 +2297,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>311463</v>
+        <v>311465</v>
       </c>
       <c r="R17" t="n">
-        <v>6525829</v>
+        <v>6525748</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2360,10 +2360,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120468030</v>
+        <v>120467979</v>
       </c>
       <c r="B18" t="n">
-        <v>57336</v>
+        <v>91542</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2372,35 +2372,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>4786</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lactifluus volemus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) Kuntze</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2408,10 +2403,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>311502</v>
+        <v>311463</v>
       </c>
       <c r="R18" t="n">
-        <v>6525831</v>
+        <v>6525779</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2452,6 +2447,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2470,10 +2466,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120467973</v>
+        <v>120467916</v>
       </c>
       <c r="B19" t="n">
-        <v>91858</v>
+        <v>79160</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2482,32 +2478,28 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -2517,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>311464</v>
+        <v>311367</v>
       </c>
       <c r="R19" t="n">
-        <v>6525792</v>
+        <v>6525824</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2580,10 +2572,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120467916</v>
+        <v>120468030</v>
       </c>
       <c r="B20" t="n">
-        <v>79160</v>
+        <v>57336</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2596,26 +2588,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2623,10 +2620,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>311367</v>
+        <v>311502</v>
       </c>
       <c r="R20" t="n">
-        <v>6525824</v>
+        <v>6525831</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2667,7 +2664,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2686,10 +2682,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120468047</v>
+        <v>120467927</v>
       </c>
       <c r="B21" t="n">
-        <v>57336</v>
+        <v>79160</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2702,31 +2698,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2734,10 +2725,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>311532</v>
+        <v>311401</v>
       </c>
       <c r="R21" t="n">
-        <v>6525858</v>
+        <v>6525852</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2778,6 +2769,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2796,10 +2788,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120468042</v>
+        <v>120467983</v>
       </c>
       <c r="B22" t="n">
-        <v>79160</v>
+        <v>90351</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2808,25 +2800,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>3215</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2839,10 +2831,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>311502</v>
+        <v>311463</v>
       </c>
       <c r="R22" t="n">
-        <v>6525831</v>
+        <v>6525779</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2902,10 +2894,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120467927</v>
+        <v>120468047</v>
       </c>
       <c r="B23" t="n">
-        <v>79160</v>
+        <v>57336</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2918,26 +2910,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2945,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>311401</v>
+        <v>311532</v>
       </c>
       <c r="R23" t="n">
-        <v>6525852</v>
+        <v>6525858</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2989,7 +2986,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3008,10 +3004,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120467944</v>
+        <v>120467973</v>
       </c>
       <c r="B24" t="n">
-        <v>57473</v>
+        <v>91858</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3020,43 +3016,34 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3064,10 +3051,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>311432</v>
+        <v>311464</v>
       </c>
       <c r="R24" t="n">
-        <v>6525830</v>
+        <v>6525792</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3102,17 +3089,13 @@
           <t>2024-10-16</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ett par i sitt hemvist och häckningsrevir</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3131,10 +3114,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120467983</v>
+        <v>120467953</v>
       </c>
       <c r="B25" t="n">
-        <v>90351</v>
+        <v>79160</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3143,25 +3126,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3215</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3177,7 +3160,7 @@
         <v>311463</v>
       </c>
       <c r="R25" t="n">
-        <v>6525779</v>
+        <v>6525829</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3237,10 +3220,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120467979</v>
+        <v>120467944</v>
       </c>
       <c r="B26" t="n">
-        <v>91542</v>
+        <v>57473</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3249,30 +3232,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4786</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lactifluus volemus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Kuntze</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3280,10 +3276,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>311463</v>
+        <v>311432</v>
       </c>
       <c r="R26" t="n">
-        <v>6525779</v>
+        <v>6525830</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3318,13 +3314,17 @@
           <t>2024-10-16</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ett par i sitt hemvist och häckningsrevir</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3343,7 +3343,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120467986</v>
+        <v>120467994</v>
       </c>
       <c r="B27" t="n">
         <v>79160</v>
@@ -3386,10 +3386,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>311465</v>
+        <v>311488</v>
       </c>
       <c r="R27" t="n">
-        <v>6525748</v>
+        <v>6525797</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3449,7 +3449,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120467994</v>
+        <v>120468042</v>
       </c>
       <c r="B28" t="n">
         <v>79160</v>
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>311488</v>
+        <v>311502</v>
       </c>
       <c r="R28" t="n">
-        <v>6525797</v>
+        <v>6525831</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>

--- a/artfynd/A 5403-2024 artfynd.xlsx
+++ b/artfynd/A 5403-2024 artfynd.xlsx
@@ -2254,10 +2254,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120467986</v>
+        <v>120467983</v>
       </c>
       <c r="B17" t="n">
-        <v>79160</v>
+        <v>90351</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2266,25 +2266,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>3215</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2297,10 +2297,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>311465</v>
+        <v>311463</v>
       </c>
       <c r="R17" t="n">
-        <v>6525748</v>
+        <v>6525779</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2360,10 +2360,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120467979</v>
+        <v>120467916</v>
       </c>
       <c r="B18" t="n">
-        <v>91542</v>
+        <v>79160</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2372,25 +2372,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4786</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lactifluus volemus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Kuntze</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>311463</v>
+        <v>311367</v>
       </c>
       <c r="R18" t="n">
-        <v>6525779</v>
+        <v>6525824</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2466,10 +2466,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120467916</v>
+        <v>120468030</v>
       </c>
       <c r="B19" t="n">
-        <v>79160</v>
+        <v>57336</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2482,26 +2482,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2509,10 +2514,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>311367</v>
+        <v>311502</v>
       </c>
       <c r="R19" t="n">
-        <v>6525824</v>
+        <v>6525831</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2553,7 +2558,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2572,10 +2576,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120468030</v>
+        <v>120467986</v>
       </c>
       <c r="B20" t="n">
-        <v>57336</v>
+        <v>79160</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2588,31 +2592,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2620,10 +2619,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>311502</v>
+        <v>311465</v>
       </c>
       <c r="R20" t="n">
-        <v>6525831</v>
+        <v>6525748</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2664,6 +2663,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2788,10 +2788,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120467983</v>
+        <v>120467994</v>
       </c>
       <c r="B22" t="n">
-        <v>90351</v>
+        <v>79160</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2800,25 +2800,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3215</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2831,10 +2831,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>311463</v>
+        <v>311488</v>
       </c>
       <c r="R22" t="n">
-        <v>6525779</v>
+        <v>6525797</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2894,10 +2894,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120468047</v>
+        <v>120467973</v>
       </c>
       <c r="B23" t="n">
-        <v>57336</v>
+        <v>91858</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2906,35 +2906,34 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2942,10 +2941,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>311532</v>
+        <v>311464</v>
       </c>
       <c r="R23" t="n">
-        <v>6525858</v>
+        <v>6525792</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2986,6 +2985,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3004,10 +3004,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120467973</v>
+        <v>120468047</v>
       </c>
       <c r="B24" t="n">
-        <v>91858</v>
+        <v>57336</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3016,34 +3016,35 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3051,10 +3052,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>311464</v>
+        <v>311532</v>
       </c>
       <c r="R24" t="n">
-        <v>6525792</v>
+        <v>6525858</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3095,7 +3096,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3114,7 +3114,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120467953</v>
+        <v>120468042</v>
       </c>
       <c r="B25" t="n">
         <v>79160</v>
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>311463</v>
+        <v>311502</v>
       </c>
       <c r="R25" t="n">
-        <v>6525829</v>
+        <v>6525831</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3220,10 +3220,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120467944</v>
+        <v>120467979</v>
       </c>
       <c r="B26" t="n">
-        <v>57473</v>
+        <v>91542</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3232,43 +3232,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>4786</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lactifluus volemus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Kuntze</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3276,10 +3263,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>311432</v>
+        <v>311463</v>
       </c>
       <c r="R26" t="n">
-        <v>6525830</v>
+        <v>6525779</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3314,17 +3301,13 @@
           <t>2024-10-16</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ett par i sitt hemvist och häckningsrevir</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3343,7 +3326,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120467994</v>
+        <v>120467953</v>
       </c>
       <c r="B27" t="n">
         <v>79160</v>
@@ -3386,10 +3369,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>311488</v>
+        <v>311463</v>
       </c>
       <c r="R27" t="n">
-        <v>6525797</v>
+        <v>6525829</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3449,10 +3432,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120468042</v>
+        <v>120467944</v>
       </c>
       <c r="B28" t="n">
-        <v>79160</v>
+        <v>57473</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3465,26 +3448,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3492,10 +3488,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>311502</v>
+        <v>311432</v>
       </c>
       <c r="R28" t="n">
-        <v>6525831</v>
+        <v>6525830</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3530,13 +3526,17 @@
           <t>2024-10-16</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ett par i sitt hemvist och häckningsrevir</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5403-2024 artfynd.xlsx
+++ b/artfynd/A 5403-2024 artfynd.xlsx
@@ -1083,7 +1083,7 @@
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG5" t="b">
         <v>0</v>

--- a/artfynd/A 5403-2024 artfynd.xlsx
+++ b/artfynd/A 5403-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115655251</v>
+        <v>115655278</v>
       </c>
       <c r="B2" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>311419</v>
+        <v>311363</v>
       </c>
       <c r="R2" t="n">
-        <v>6525722</v>
+        <v>6525566</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Relativt färska hack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115655270</v>
+        <v>115655279</v>
       </c>
       <c r="B3" t="n">
-        <v>57284</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102977</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>311295</v>
+        <v>311404</v>
       </c>
       <c r="R3" t="n">
-        <v>6525465</v>
+        <v>6526037</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Läte</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115655249</v>
+        <v>115655280</v>
       </c>
       <c r="B4" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>311365</v>
+        <v>311317</v>
       </c>
       <c r="R4" t="n">
-        <v>6525654</v>
+        <v>6525337</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115655238</v>
+        <v>115655247</v>
       </c>
       <c r="B5" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>2569</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>311399</v>
+        <v>311378</v>
       </c>
       <c r="R5" t="n">
-        <v>6525746</v>
+        <v>6525633</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,16 +1039,11 @@
           <t>2024-03-30</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="b">
         <v>0</v>
@@ -1106,12 +1066,7 @@
         <v>115655231</v>
       </c>
       <c r="B6" t="n">
-        <v>94069</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115655276</v>
+        <v>120467983</v>
       </c>
       <c r="B7" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,37 +1171,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>3215</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bön, Dls</t>
+          <t>Keddebo-Bön, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>311408</v>
+        <v>311463</v>
       </c>
       <c r="R7" t="n">
-        <v>6525585</v>
+        <v>6525779</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1275,12 +1228,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1289,55 +1242,51 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115655279</v>
+        <v>115655276</v>
       </c>
       <c r="B8" t="n">
-        <v>94429</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1296,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>311404</v>
+        <v>311408</v>
       </c>
       <c r="R8" t="n">
-        <v>6526037</v>
+        <v>6525585</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,53 +1358,55 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115655242</v>
+        <v>120467973</v>
       </c>
       <c r="B9" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bön, Dls</t>
+          <t>Keddebo-Bön, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>311276</v>
+        <v>311464</v>
       </c>
       <c r="R9" t="n">
-        <v>6525528</v>
+        <v>6525792</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1479,17 +1430,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1498,71 +1444,70 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115655253</v>
+        <v>120467979</v>
       </c>
       <c r="B10" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92905</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>4786</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lactifluus volemus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kuntze</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bön, Dls</t>
+          <t>Keddebo-Bön, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>311415</v>
+        <v>311463</v>
       </c>
       <c r="R10" t="n">
-        <v>6525592</v>
+        <v>6525779</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1586,17 +1531,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1605,71 +1545,70 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115655278</v>
+        <v>120467916</v>
       </c>
       <c r="B11" t="n">
-        <v>94429</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bön, Dls</t>
+          <t>Keddebo-Bön, Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>311363</v>
+        <v>311367</v>
       </c>
       <c r="R11" t="n">
-        <v>6525566</v>
+        <v>6525824</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1693,12 +1632,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1707,71 +1646,70 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115655280</v>
+        <v>120467927</v>
       </c>
       <c r="B12" t="n">
-        <v>94429</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bön, Dls</t>
+          <t>Keddebo-Bön, Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>311317</v>
+        <v>311401</v>
       </c>
       <c r="R12" t="n">
-        <v>6525337</v>
+        <v>6525852</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1795,12 +1733,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1809,71 +1747,70 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115655269</v>
+        <v>120467953</v>
       </c>
       <c r="B13" t="n">
-        <v>57284</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102977</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bön, Dls</t>
+          <t>Keddebo-Bön, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>311318</v>
+        <v>311463</v>
       </c>
       <c r="R13" t="n">
-        <v>6525537</v>
+        <v>6525829</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1897,17 +1834,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Sång</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1916,71 +1848,70 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>115655247</v>
+        <v>120467986</v>
       </c>
       <c r="B14" t="n">
-        <v>95923</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2569</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bön, Dls</t>
+          <t>Keddebo-Bön, Dls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>311378</v>
+        <v>311465</v>
       </c>
       <c r="R14" t="n">
-        <v>6525633</v>
+        <v>6525748</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2004,12 +1935,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2018,33 +1949,29 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>115655254</v>
+        <v>120467994</v>
       </c>
       <c r="B15" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2052,37 +1979,40 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bön, Dls</t>
+          <t>Keddebo-Bön, Dls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>311417</v>
+        <v>311488</v>
       </c>
       <c r="R15" t="n">
-        <v>6525623</v>
+        <v>6525797</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2106,17 +2036,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2125,33 +2050,29 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>115655239</v>
+        <v>120468042</v>
       </c>
       <c r="B16" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2159,41 +2080,40 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bön, Dls</t>
+          <t>Keddebo-Bön, Dls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>311442</v>
+        <v>311502</v>
       </c>
       <c r="R16" t="n">
-        <v>6525614</v>
+        <v>6525831</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2217,17 +2137,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2236,74 +2151,67 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120467986</v>
+        <v>115655249</v>
       </c>
       <c r="B17" t="n">
-        <v>79208</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Keddebo-Bön, Dls</t>
+          <t>Bön, Dls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>311465</v>
+        <v>311365</v>
       </c>
       <c r="R17" t="n">
-        <v>6525748</v>
+        <v>6525654</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2327,12 +2235,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2341,34 +2254,28 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120467983</v>
+        <v>115655251</v>
       </c>
       <c r="B18" t="n">
-        <v>90441</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2376,40 +2283,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3215</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Keddebo-Bön, Dls</t>
+          <t>Bön, Dls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>311463</v>
+        <v>311419</v>
       </c>
       <c r="R18" t="n">
-        <v>6525779</v>
+        <v>6525722</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2433,12 +2337,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Relativt färska hack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2447,34 +2356,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120467979</v>
+        <v>115655253</v>
       </c>
       <c r="B19" t="n">
-        <v>91632</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2482,40 +2385,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4786</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lactifluus volemus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Kuntze</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Keddebo-Bön, Dls</t>
+          <t>Bön, Dls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>311463</v>
+        <v>311415</v>
       </c>
       <c r="R19" t="n">
-        <v>6525779</v>
+        <v>6525592</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2539,12 +2439,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2553,75 +2458,66 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120467953</v>
+        <v>115655254</v>
       </c>
       <c r="B20" t="n">
-        <v>79208</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Keddebo-Bön, Dls</t>
+          <t>Bön, Dls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>311463</v>
+        <v>311417</v>
       </c>
       <c r="R20" t="n">
-        <v>6525829</v>
+        <v>6525623</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2645,12 +2541,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2659,38 +2560,32 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120468047</v>
+        <v>120468030</v>
       </c>
       <c r="B21" t="n">
-        <v>57360</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2726,10 +2621,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>311532</v>
+        <v>311502</v>
       </c>
       <c r="R21" t="n">
-        <v>6525858</v>
+        <v>6525831</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2788,42 +2683,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120468042</v>
+        <v>120468047</v>
       </c>
       <c r="B22" t="n">
-        <v>79208</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2831,10 +2726,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>311502</v>
+        <v>311532</v>
       </c>
       <c r="R22" t="n">
-        <v>6525831</v>
+        <v>6525858</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2875,7 +2770,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2894,15 +2788,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120467973</v>
+        <v>120468509</v>
       </c>
       <c r="B23" t="n">
-        <v>91945</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2910,30 +2799,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2941,10 +2831,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>311464</v>
+        <v>311510</v>
       </c>
       <c r="R23" t="n">
-        <v>6525792</v>
+        <v>6525929</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2985,7 +2875,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3004,15 +2893,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120467916</v>
+        <v>115655238</v>
       </c>
       <c r="B24" t="n">
-        <v>79208</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3020,40 +2904,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Keddebo-Bön, Dls</t>
+          <t>Bön, Dls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>311367</v>
+        <v>311399</v>
       </c>
       <c r="R24" t="n">
-        <v>6525824</v>
+        <v>6525746</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3077,48 +2958,47 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF24" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120467994</v>
+        <v>115655239</v>
       </c>
       <c r="B25" t="n">
-        <v>79208</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3126,40 +3006,41 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Keddebo-Bön, Dls</t>
+          <t>Bön, Dls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>311488</v>
+        <v>311442</v>
       </c>
       <c r="R25" t="n">
-        <v>6525797</v>
+        <v>6525614</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3183,12 +3064,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3197,88 +3083,66 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120467944</v>
+        <v>115655242</v>
       </c>
       <c r="B26" t="n">
-        <v>57497</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Keddebo-Bön, Dls</t>
+          <t>Bön, Dls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>311432</v>
+        <v>311276</v>
       </c>
       <c r="R26" t="n">
-        <v>6525830</v>
+        <v>6525528</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3302,17 +3166,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ett par i sitt hemvist och häckningsrevir</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3327,68 +3191,60 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120467927</v>
+        <v>115655269</v>
       </c>
       <c r="B27" t="n">
-        <v>79208</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>102977</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Keddebo-Bön, Dls</t>
+          <t>Bön, Dls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>311401</v>
+        <v>311318</v>
       </c>
       <c r="R27" t="n">
-        <v>6525852</v>
+        <v>6525537</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3412,12 +3268,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3426,80 +3287,66 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120468030</v>
+        <v>115655270</v>
       </c>
       <c r="B28" t="n">
-        <v>57360</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>102977</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Keddebo-Bön, Dls</t>
+          <t>Bön, Dls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>311502</v>
+        <v>311295</v>
       </c>
       <c r="R28" t="n">
-        <v>6525831</v>
+        <v>6525465</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3523,12 +3370,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3543,15 +3395,133 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120467944</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Keddebo-Bön, Dls</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>311432</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6525830</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Töftedal</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ett par i sitt hemvist och häckningsrevir</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
           <t>Steve Daurer</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
+      <c r="AX29" t="inlineStr">
         <is>
           <t>Steve Daurer</t>
         </is>
       </c>
-      <c r="AY28" t="inlineStr"/>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5403-2024 artfynd.xlsx
+++ b/artfynd/A 5403-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115655278</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115655279</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115655280</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115655247</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115655231</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467983</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1355,6 +1390,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115655276</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1460,6 +1500,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467973</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1561,6 +1606,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467979</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1662,6 +1712,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467916</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1763,6 +1818,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467927</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1864,6 +1924,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467953</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1965,6 +2030,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467986</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2066,6 +2136,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467994</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2167,6 +2242,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120468042</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2269,6 +2349,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115655249</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2371,6 +2456,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115655251</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2473,6 +2563,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115655253</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2575,6 +2670,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115655254</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2680,6 +2780,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120468030</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2785,6 +2890,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120468047</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2890,6 +3000,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120468509</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2992,6 +3107,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115655238</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3098,6 +3218,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115655239</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3200,6 +3325,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115655242</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3302,6 +3432,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115655269</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3404,6 +3539,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115655270</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3522,8 +3662,43 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467944</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>